--- a/260508_Coord_nodes_SWMM.xlsx
+++ b/260508_Coord_nodes_SWMM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pierre-Yves\Documents\EPA SWMM Projects\Twann_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ISSKA\Documents\GitHub\Twanntunnel_Hydraulic_SWMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A68AF4-79D5-4B41-8F2F-A96ED03FF144}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882AFE1A-18AF-4F60-9FDC-3D4CBD85339A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20235" windowHeight="9060" xr2:uid="{5560F17C-8740-4256-B354-A6A3ABF31B82}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>Holiloch_sonde</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Longueur depuis portail Est:</t>
   </si>
   <si>
-    <t>TWT_PointHaut_60+650</t>
-  </si>
-  <si>
     <t>TWT_Portail_Est_61+665</t>
   </si>
   <si>
@@ -214,6 +211,9 @@
   </si>
   <si>
     <t>SonSto_porte</t>
+  </si>
+  <si>
+    <t>TWT_PointHaut_60+749</t>
   </si>
 </sst>
 </file>
@@ -714,6 +714,9 @@
       <c r="C9">
         <v>1215862</v>
       </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1341,6 +1344,9 @@
       <c r="C54">
         <v>1215879</v>
       </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
@@ -1391,7 +1397,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60">
         <v>2578941.7599999998</v>
@@ -1405,7 +1411,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61">
         <v>2578918.5099999998</v>
@@ -1418,24 +1424,24 @@
       </c>
       <c r="F61" s="5">
         <f>B61-B78</f>
-        <v>469.50999999977648</v>
+        <v>358.50999999977648</v>
       </c>
       <c r="G61" s="5">
         <f>C61-C78</f>
-        <v>245.26000000000931</v>
+        <v>139.26000000000931</v>
       </c>
       <c r="H61">
         <f>SQRT((F61*F61)+(G61*G61))</f>
-        <v>529.70945592824251</v>
+        <v>384.60729023231255</v>
       </c>
       <c r="I61">
         <f>SQRT((H61*H61)+(3.3*3.3))</f>
-        <v>529.71973504844493</v>
+        <v>384.62144726970484</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5">
         <v>2578995.19</v>
@@ -1449,7 +1455,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B63" s="3">
         <v>2578239</v>
@@ -1469,7 +1475,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B64">
         <v>2578234</v>
@@ -1485,7 +1491,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B65" s="3">
         <v>2578202</v>
@@ -1568,7 +1574,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B72" s="3">
         <v>2579848</v>
@@ -1672,13 +1678,13 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B78" s="3">
-        <v>2578449</v>
+        <v>2578560</v>
       </c>
       <c r="C78" s="3">
-        <v>1216034</v>
+        <v>1216140</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3">
@@ -1730,7 +1736,7 @@
         <v>437.3</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J80">
         <v>275</v>
@@ -1772,7 +1778,7 @@
         <v>437.5</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J82">
         <v>265</v>
@@ -1796,7 +1802,7 @@
         <v>446.5</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J83">
         <v>348</v>

--- a/260508_Coord_nodes_SWMM.xlsx
+++ b/260508_Coord_nodes_SWMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ISSKA\Documents\GitHub\Twanntunnel_Hydraulic_SWMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882AFE1A-18AF-4F60-9FDC-3D4CBD85339A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A11C5CA-95B3-4FB7-A32B-1ACCB278A640}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20235" windowHeight="9060" xr2:uid="{5560F17C-8740-4256-B354-A6A3ABF31B82}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
   <si>
     <t>Holiloch_sonde</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>TWT_PointHaut_60+749</t>
+  </si>
+  <si>
+    <t>CentraleVentilation_1C</t>
   </si>
 </sst>
 </file>
@@ -586,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336D857F-22C8-4624-8585-90FCE8727574}">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1808,6 +1811,22 @@
         <v>348</v>
       </c>
     </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2578077</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1215700</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3">
+        <v>454</v>
+      </c>
+      <c r="F84" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
